--- a/myPortfolio_Yahoo_Restore_20261018.xlsx
+++ b/myPortfolio_Yahoo_Restore_20261018.xlsx
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B19" s="60" t="inlineStr">
         <is>
-          <t>CSOP Hang Seng TECH Index Daily (-2x) Inverse Product</t>
+          <t>Hang Seng JPMorgan US Equity Premium Income Active ETF</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B20" s="56" t="inlineStr">
         <is>
-          <t>CSOP FTSE China A50 Index ETF</t>
+          <t>CSOP FTSE US Treasury 20+ Years Index ETF</t>
         </is>
       </c>
       <c r="C20" s="56" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B22" s="56" t="inlineStr">
         <is>
-          <t>CSOP Hang Seng Index Daily (-1x) Inverse Product</t>
+          <t>Hang Seng S&amp;P 500 Index ETF</t>
         </is>
       </c>
       <c r="C22" s="56" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="B19" s="60" t="inlineStr">
         <is>
-          <t>CSOP Hang Seng TECH Index Daily (-2x) Inverse Product</t>
+          <t>Hang Seng JPMorgan US Equity Premium Income Active ETF</t>
         </is>
       </c>
       <c r="C19" s="60" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B20" s="56" t="inlineStr">
         <is>
-          <t>CSOP FTSE China A50 Index ETF</t>
+          <t>CSOP FTSE US Treasury 20+ Years Index ETF</t>
         </is>
       </c>
       <c r="C20" s="56" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="B22" s="56" t="inlineStr">
         <is>
-          <t>CSOP Hang Seng Index Daily (-1x) Inverse Product</t>
+          <t>Hang Seng S&amp;P 500 Index ETF</t>
         </is>
       </c>
       <c r="C22" s="56" t="inlineStr">
